--- a/artfynd/A 16845-2025 artfynd.xlsx
+++ b/artfynd/A 16845-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62023315</v>
+        <v>119640226</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stugusjön, Jmt</t>
+          <t>Stenloken, väster om, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509177.1156600881</v>
+        <v>508820</v>
       </c>
       <c r="R2" t="n">
-        <v>7003896.762096249</v>
+        <v>7003985</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-10-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-10-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>140-årig gallrad stavatallskog på småblockig rismark</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -782,37 +767,36 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>1 substratenheter # mycket grov gammal tallåga av yxfälld urskogstall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg, Sven Bengtsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119640210</v>
+        <v>119640221</v>
       </c>
       <c r="B3" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -836,14 +820,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stenloken, söder om, Jmt</t>
+          <t>Stenloken, väster om, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509407</v>
+        <v>508746</v>
       </c>
       <c r="R3" t="n">
-        <v>7003470</v>
+        <v>7003960</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +873,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>140-årig gallrad stavatallskog på småblockig rismark</t>
+          <t>140-årig ogallrad stavatallskog på småblockig mark med lavfläckar</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -911,37 +895,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119640227</v>
+        <v>119640225</v>
       </c>
       <c r="B4" t="n">
-        <v>92030</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509124</v>
+        <v>508592</v>
       </c>
       <c r="R4" t="n">
-        <v>7003963</v>
+        <v>7004028</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,15 +979,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>140-årig gallrad stavatallskog på blockig mark, spridd gammal tall</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>1 substratenheter # tallåga av fallen torraka</t>
+          <t>140-årig gallrad stavatallskog på småblockig mark med lavfläckar</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1030,15 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119640211</v>
+        <v>62023319</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,34 +1012,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenloken, söder om, Jmt</t>
+          <t>Stugusjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509407</v>
+        <v>508791</v>
       </c>
       <c r="R5" t="n">
-        <v>7003470</v>
+        <v>7003810</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,12 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,37 +1085,36 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>140-årig gallrad stavatallskog på småblockig rismark</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter # sälg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Johan Kjetselberg, Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119640245</v>
+        <v>119640214</v>
       </c>
       <c r="B6" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,34 +1122,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stenloken, sydväst om, Jmt</t>
+          <t>Stenloken, väster om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509260</v>
+        <v>508960</v>
       </c>
       <c r="R6" t="n">
-        <v>7003809</v>
+        <v>7003796</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1195,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>140-årig stavatallskog på blockig mark med lavfläckar</t>
+          <t>140-årig gallrad stavatallskog på blockig mark med spridd äldre tall</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -1238,7 +1203,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>1 substratenheter # gammal tallågerest</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1260,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119640269</v>
+        <v>119640216</v>
       </c>
       <c r="B7" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,14 +1256,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenloken, söder om, Jmt</t>
+          <t>Stenloken, väster om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509447</v>
+        <v>508957</v>
       </c>
       <c r="R7" t="n">
-        <v>7003629</v>
+        <v>7003853</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1309,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>140-årig senvuxen tallskog på blockig mark</t>
+          <t>140-årig gallrad stavatallskog på blockig mark med spridd äldre tall</t>
         </is>
       </c>
       <c r="AN7" t="n">
@@ -1357,7 +1317,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallåga efter lumpad tall</t>
+          <t>1 substratenheter # grov gammal tallåga</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1379,15 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119640226</v>
+        <v>119640228</v>
       </c>
       <c r="B8" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1419,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>508820</v>
+        <v>509124</v>
       </c>
       <c r="R8" t="n">
-        <v>7003985</v>
+        <v>7003963</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,7 +1423,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>140-årig gallrad stavatallskog på småblockig rismark</t>
+          <t>140-årig gallrad stavatallskog på blockig mark, spridd gammal tall</t>
         </is>
       </c>
       <c r="AN8" t="n">
@@ -1476,7 +1431,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # mycket grov gammal tallåga av yxfälld urskogstall</t>
+          <t>1 substratenheter # tallåga av fallen torraka</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1498,15 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119640268</v>
+        <v>119640229</v>
       </c>
       <c r="B9" t="n">
-        <v>79115</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,34 +1464,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stenloken, söder om, Jmt</t>
+          <t>Stenloken, väster om, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509472</v>
+        <v>509067</v>
       </c>
       <c r="R9" t="n">
-        <v>7003666</v>
+        <v>7003975</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,15 +1537,15 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>140-årig senvuxen tallskog på blockig mark</t>
+          <t>140-årig gallrad stavatallskog på blockig mark, spridd gammal tall</t>
         </is>
       </c>
       <c r="AN9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>2 substratenheter # rotben av gammal grov tallågerest och skorstenshögstubbe</t>
+          <t>1 substratenheter # mycket grov tallåga av sedan länge fallen högstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1617,15 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119640239</v>
+        <v>119640235</v>
       </c>
       <c r="B10" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509299</v>
+        <v>509199</v>
       </c>
       <c r="R10" t="n">
-        <v>7003527</v>
+        <v>7003583</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1714,7 +1659,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallågerest</t>
+          <t>1 substratenheter # gammalt grovt tallvindfälle</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1736,15 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119640229</v>
+        <v>119640239</v>
       </c>
       <c r="B11" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,14 +1712,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenloken, väster om, Jmt</t>
+          <t>Stenloken, sydväst om, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509067</v>
+        <v>509299</v>
       </c>
       <c r="R11" t="n">
-        <v>7003975</v>
+        <v>7003527</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1765,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>140-årig gallrad stavatallskog på blockig mark, spridd gammal tall</t>
+          <t>140-årig gallrad stavatallskog på blockig mark med lavfläckar</t>
         </is>
       </c>
       <c r="AN11" t="n">
@@ -1833,7 +1773,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>1 substratenheter # mycket grov tallåga av sedan länge fallen högstubbe</t>
+          <t>1 substratenheter # gammal tallågerest</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1855,15 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119640264</v>
+        <v>119640247</v>
       </c>
       <c r="B12" t="n">
-        <v>80483</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,34 +1806,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stenloken, söder om, Jmt</t>
+          <t>Stenloken, sydväst om, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509481</v>
+        <v>509269</v>
       </c>
       <c r="R12" t="n">
-        <v>7003819</v>
+        <v>7003875</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1944,7 +1879,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>140-årig senvuxen tallskog på blockig mark med lavfläckar</t>
+          <t>160-årig tallskog på blockig mark intill lok</t>
         </is>
       </c>
       <c r="AN12" t="n">
@@ -1952,7 +1887,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1 substratenheter # vitrötad gammal tallhögstubbe med spår av tre bränder</t>
+          <t>1 substratenheter # grovt gammalt tallvindfälle</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1974,15 +1909,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119640230</v>
+        <v>119640248</v>
       </c>
       <c r="B13" t="n">
-        <v>78263</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,34 +1920,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stenloken, väster om, Jmt</t>
+          <t>Stenloken, sydväst om, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509051</v>
+        <v>509290</v>
       </c>
       <c r="R13" t="n">
-        <v>7003964</v>
+        <v>7003837</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2063,7 +1993,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>140-årig gallrad stavatallskog på blockig mark med lavfläckar</t>
+          <t>140-årig stavatallskog på blockig mark med lavfläckar</t>
         </is>
       </c>
       <c r="AN13" t="n">
@@ -2071,7 +2001,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>1 substratenheter # grova brandstubbar</t>
+          <t>1 substratenheter # gamla tallågor upphängda på block</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2093,15 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119640225</v>
+        <v>119640269</v>
       </c>
       <c r="B14" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,34 +2034,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stenloken, väster om, Jmt</t>
+          <t>Stenloken, söder om, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>508592</v>
+        <v>509447</v>
       </c>
       <c r="R14" t="n">
-        <v>7004028</v>
+        <v>7003629</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2182,7 +2107,15 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>140-årig gallrad stavatallskog på småblockig mark med lavfläckar</t>
+          <t>140-årig senvuxen tallskog på blockig mark</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga efter lumpad tall</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2204,15 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119640212</v>
+        <v>119640287</v>
       </c>
       <c r="B15" t="n">
-        <v>91832</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2220,34 +2148,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stenloken, sydväst om, Jmt</t>
+          <t>Orrviktjärnen, norr om, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509291</v>
+        <v>508935</v>
       </c>
       <c r="R15" t="n">
-        <v>7003510</v>
+        <v>7003749</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2274,12 +2202,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,7 +2221,15 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>140-årig gallrad stavatallskog på småblockig rismark</t>
+          <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal torr tallåga</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2315,15 +2251,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119640228</v>
+        <v>119640261</v>
       </c>
       <c r="B16" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2331,34 +2262,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stenloken, väster om, Jmt</t>
+          <t>Stenloken, sydväst om, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509124</v>
+        <v>509363</v>
       </c>
       <c r="R16" t="n">
-        <v>7003963</v>
+        <v>7003786</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2404,7 +2335,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>140-årig gallrad stavatallskog på blockig mark, spridd gammal tall</t>
+          <t>140-årig senvuxen tallskog på blockig mark med lavfläckar</t>
         </is>
       </c>
       <c r="AN16" t="n">
@@ -2412,7 +2343,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>1 substratenheter # tallåga av fallen torraka</t>
+          <t>1 substratenheter # vitrötad gammal grov tallhögstubbe</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2434,15 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119640214</v>
+        <v>119640264</v>
       </c>
       <c r="B17" t="n">
-        <v>78171</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2450,34 +2376,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stenloken, väster om, Jmt</t>
+          <t>Stenloken, söder om, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>508960</v>
+        <v>509481</v>
       </c>
       <c r="R17" t="n">
-        <v>7003796</v>
+        <v>7003819</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2523,7 +2449,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>140-årig gallrad stavatallskog på blockig mark med spridd äldre tall</t>
+          <t>140-årig senvuxen tallskog på blockig mark med lavfläckar</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -2531,7 +2457,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal tallågerest</t>
+          <t>1 substratenheter # vitrötad gammal tallhögstubbe med spår av tre bränder</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2553,19 +2479,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119640213</v>
+        <v>119640210</v>
       </c>
       <c r="B18" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2589,14 +2510,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenloken, sydväst om, Jmt</t>
+          <t>Stenloken, söder om, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509031</v>
+        <v>509407</v>
       </c>
       <c r="R18" t="n">
-        <v>7003714</v>
+        <v>7003470</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2642,12 +2563,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>140-årig gallrad stavatallskog på blockig mark med spridd äldre tall</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>gammal drivningsväg i 140-årig tallskog på morän</t>
+          <t>140-årig gallrad stavatallskog på småblockig rismark</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2669,37 +2585,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119640240</v>
+        <v>119640213</v>
       </c>
       <c r="B19" t="n">
-        <v>5485</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101410</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2709,10 +2620,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509367</v>
+        <v>509031</v>
       </c>
       <c r="R19" t="n">
-        <v>7003402</v>
+        <v>7003714</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2758,15 +2669,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>140-årig tallskog på blockig mark med lavfläckar och inslag av gammal tall</t>
-        </is>
-      </c>
-      <c r="AN19" t="n">
-        <v>1</v>
+          <t>140-årig gallrad stavatallskog på blockig mark med spridd äldre tall</t>
+        </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>1 substratenheter # typiska spår i drygt 200-årig tall</t>
+          <t>gammal drivningsväg i 140-årig tallskog på morän</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2788,19 +2696,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119640266</v>
+        <v>119640231</v>
       </c>
       <c r="B20" t="n">
-        <v>91856</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2824,14 +2727,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stenloken, söder om, Jmt</t>
+          <t>Stenloken, väster om, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509465</v>
+        <v>509033</v>
       </c>
       <c r="R20" t="n">
-        <v>7003790</v>
+        <v>7003909</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2877,12 +2780,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>140-årig senvuxen tallskog på blockig mark med lavfläckar</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>rotben av gammal grov tallågerest och skorstenshögstubbe</t>
+          <t>gammal drivningsväg i 140-årig gallrad stavatallskog på blockig mark med lavfläckar</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2897,6 +2795,1686 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>119640245</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93213</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stenloken, sydväst om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>509260</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7003809</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>140-årig stavatallskog på blockig mark med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>119640246</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93213</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stenloken, sydväst om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>509262</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7003864</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>140-årig stavatallskog på blockig mark med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>119640266</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93213</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stenloken, söder om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>509465</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7003790</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>140-årig senvuxen tallskog på blockig mark med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>rotben av gammal grov tallågerest och skorstenshögstubbe</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>119640343</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93213</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Orrviktjärnen, öster om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>509352</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7003312</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>140-årig tallskog på småblockig morän med lav</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>119640227</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stenloken, väster om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>509124</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7003963</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>140-årig gallrad stavatallskog på blockig mark, spridd gammal tall</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>1 substratenheter # tallåga av fallen torraka</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>119640232</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stenloken, väster om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>509101</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7003877</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>140-årig gallrad stavatallskog på blockig mark med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal, halvt nermurken tallåga</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>119640212</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stenloken, sydväst om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>509291</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7003510</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>140-årig gallrad stavatallskog på småblockig rismark</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>62023315</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stugusjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>509177</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7003897</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2016-10-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2016-10-24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg, Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>62023317</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stugusjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>509154</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7003612</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2016-10-24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2016-10-24</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg, Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>119640240</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stenloken, sydväst om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>509367</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7003402</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>140-årig tallskog på blockig mark med lavfläckar och inslag av gammal tall</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>1 substratenheter # typiska spår i drygt 200-årig tall</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>119640230</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stenloken, väster om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>509051</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7003964</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>140-årig gallrad stavatallskog på blockig mark med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grova brandstubbar</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>119640238</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stenloken, sydväst om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>509286</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7003576</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>140-årig gallrad stavatallskog på blockig mark med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>brandstubbar</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>119640249</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stenloken, sydväst om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>509270</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7003786</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>140-årig stavatallskog på blockig mark med lavfläckar</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>119640263</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stenloken, sydväst om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>509354</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7003807</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>140-årig senvuxen tallskog på blockig mark</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>1 substratenheter # vitmurken grov skorstenshögstubbe</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>119640268</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stenloken, söder om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>509472</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7003666</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>140-årig senvuxen tallskog på blockig mark</t>
+        </is>
+      </c>
+      <c r="AN35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>2 substratenheter # rotben av gammal grov tallågerest och skorstenshögstubbe</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
